--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484615_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484615_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7597</v>
+        <v>4.1939</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5224</v>
+        <v>5.907</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7626</v>
+        <v>-1.7131</v>
       </c>
       <c r="G2" t="n">
         <v>4.2607</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5167</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4404</v>
+        <v>-0.0558</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0268</v>
       </c>
       <c r="V2" t="n">
         <v>-1.267</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5644</v>
+        <v>-1.4683</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1085</v>
+        <v>-0.0124</v>
       </c>
       <c r="F5" t="n">
         <v>-1.4559</v>
@@ -844,10 +844,10 @@
         <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4216</v>
+        <v>-0.3254</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U5" t="n">
         <v>-0.2564</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9535</v>
+        <v>-2.4561</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5802</v>
+        <v>-1.1571</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3733</v>
+        <v>-1.299</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5521</v>
@@ -922,13 +922,13 @@
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6536</v>
+        <v>0.151</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8416</v>
+        <v>0.2647</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.188</v>
+        <v>-0.1137</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9554</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7776</v>
+        <v>-2.7281</v>
       </c>
       <c r="E7" t="n">
         <v>-0.8366</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.941</v>
+        <v>-1.8915</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0037</v>
@@ -1000,13 +1000,13 @@
         <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7739</v>
+        <v>-0.7244</v>
       </c>
       <c r="T7" t="n">
         <v>0.0717</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8456</v>
+        <v>-0.796</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6335</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CLIMENT GOMIS</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.049</v>
+        <v>-2.7898</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6086</v>
+        <v>-0.4674</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4404</v>
+        <v>-2.3224</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3521</v>
+        <v>-2.4739</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.2687</v>
+        <v>-1.3133</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0833</v>
+        <v>-1.1605</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7187</v>
+        <v>1.6921</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.437</v>
+        <v>0.8328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7183</v>
+        <v>0.8592</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6333</v>
+        <v>-4.1659</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8317</v>
+        <v>-2.1462</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8017</v>
+        <v>-2.0198</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0465</v>
+        <v>-0.316</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6757</v>
+        <v>-0.3269</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6293</v>
+        <v>0.0109</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>J. CLIMENT GOMIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.177</v>
+        <v>-3.4307</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0032</v>
+        <v>-1.0894</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1738</v>
+        <v>-2.3414</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4739</v>
+        <v>-3.3521</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3133</v>
+        <v>-3.2687</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1605</v>
+        <v>-0.0833</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6921</v>
+        <v>-0.7187</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8328</v>
+        <v>-1.437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8592</v>
+        <v>0.7183</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1659</v>
+        <v>-2.6333</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1462</v>
+        <v>-1.8317</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0198</v>
+        <v>-0.8017</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7032</v>
+        <v>-0.3352</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8627</v>
+        <v>0.195</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1596</v>
+        <v>-0.5302</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5797</v>
+        <v>-3.6802</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4295</v>
+        <v>-0.9831</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1502</v>
+        <v>-2.6972</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1771</v>
+        <v>0.6</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2857</v>
+        <v>-1.1888</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8914</v>
+        <v>1.7888</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0179</v>
+        <v>3.4989</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8512</v>
+        <v>0.7803</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1667</v>
+        <v>2.7187</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.195</v>
+        <v>-2.899</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.137</v>
+        <v>-1.9691</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0581</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.733</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5766</v>
+        <v>-0.9529</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5475</v>
+        <v>-0.1938</v>
       </c>
       <c r="U10" t="n">
-        <v>0.029</v>
+        <v>-0.7591</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2461</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.2461</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6916</v>
+        <v>-3.9921</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8458</v>
+        <v>-2.718</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8458</v>
+        <v>-1.2741</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>-2.1771</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1888</v>
+        <v>-1.2857</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7888</v>
+        <v>-0.8914</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4989</v>
+        <v>1.0179</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7803</v>
+        <v>0.8512</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7187</v>
+        <v>0.1667</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.899</v>
+        <v>-3.195</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9691</v>
+        <v>-2.137</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.0581</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3823</v>
+        <v>-0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2828</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9641999999999999</v>
+        <v>0.1642</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0565</v>
+        <v>0.2591</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9077</v>
+        <v>-0.0948</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.945</v>
+        <v>-1.2461</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6231</v>
+        <v>-1.2461</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9643</v>
+        <v>-4.4503</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4939</v>
+        <v>-2.0542</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4704</v>
+        <v>-2.3961</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5138</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4897</v>
+        <v>-0.9757</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8077</v>
+        <v>-0.368</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6077</v>
       </c>
       <c r="V12" t="n">
         <v>0.9554</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8416</v>
+        <v>-5.9906</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9992</v>
+        <v>-2.7518</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8424</v>
+        <v>-3.2388</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1914</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5561</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6425</v>
+        <v>-0.3952</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0864</v>
+        <v>-0.31</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9109</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.0999</v>
+        <v>-7.4102</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.1697</v>
+        <v>-3.5543</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.9303</v>
+        <v>-3.8559</v>
       </c>
       <c r="G14" t="n">
         <v>-5.1012</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2683</v>
+        <v>-0.042</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6576</v>
+        <v>0.273</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3894</v>
+        <v>-0.3151</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9005</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.4374</v>
+        <v>-7.8986</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.7906</v>
+        <v>-4.3509</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.6468</v>
+        <v>-3.5477</v>
       </c>
       <c r="G15" t="n">
         <v>-7.1995</v>
@@ -1624,13 +1624,13 @@
         <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0704</v>
+        <v>-0.5317</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5694</v>
+        <v>-0.1297</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5011</v>
+        <v>-0.402</v>
       </c>
       <c r="V15" t="n">
         <v>-1.267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-40.1508</v>
+        <v>-39.8756</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.1179</v>
+        <v>-11.8427</v>
       </c>
       <c r="F16" t="n">
-        <v>-28.0329</v>
+        <v>-28.0331</v>
       </c>
       <c r="G16" t="n">
         <v>-22.666</v>
@@ -1693,7 +1693,7 @@
         <v>-9.939899999999998</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.6651</v>
+        <v>-3.665100000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>-20.1585</v>
@@ -1702,13 +1702,13 @@
         <v>16.4932</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.9508</v>
+        <v>-4.6758</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7503000000000001</v>
+        <v>-0.4749000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.2008</v>
+        <v>-4.200900000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-8.8688</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>9.642799999999999</v>
+        <v>9.3283</v>
       </c>
       <c r="E17" t="n">
-        <v>7.2376</v>
+        <v>7.9097</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4052</v>
+        <v>1.4186</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7938</v>
+        <v>7.3523</v>
       </c>
       <c r="H17" t="n">
-        <v>6.0089</v>
+        <v>2.5175</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2151</v>
+        <v>4.8348</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3574</v>
+        <v>8.093</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5145</v>
+        <v>2.3283</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.157</v>
+        <v>5.7647</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5636</v>
+        <v>-0.7407</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4944</v>
+        <v>0.1891</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0581</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6816</v>
+        <v>0.5545</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1787</v>
+        <v>0.411</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5028</v>
+        <v>0.1435</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>7.6396</v>
+        <v>7.9001</v>
       </c>
       <c r="E18" t="n">
-        <v>6.9482</v>
+        <v>6.1799</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6915</v>
+        <v>1.7203</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3523</v>
+        <v>3.7938</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5175</v>
+        <v>6.0089</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8348</v>
+        <v>-2.2151</v>
       </c>
       <c r="J18" t="n">
-        <v>8.093</v>
+        <v>4.3574</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3283</v>
+        <v>5.5145</v>
       </c>
       <c r="L18" t="n">
-        <v>5.7647</v>
+        <v>-1.157</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7407</v>
+        <v>-0.5636</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1891</v>
+        <v>0.4944</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.0581</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0995</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1342</v>
+        <v>1.9389</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5505</v>
+        <v>1.1211</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5836</v>
+        <v>0.8178</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3219</v>
+        <v>2.5339</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>2.5339</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.0301</v>
+        <v>5.8596</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9395</v>
+        <v>2.8434</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0905</v>
+        <v>3.0162</v>
       </c>
       <c r="G19" t="n">
         <v>3.5742</v>
@@ -1936,13 +1936,13 @@
         <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0319</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5664</v>
+        <v>0.4702</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4655</v>
+        <v>0.3912</v>
       </c>
       <c r="V19" t="n">
         <v>2.5235</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5.2408</v>
+        <v>4.9887</v>
       </c>
       <c r="E20" t="n">
-        <v>4.9642</v>
+        <v>4.5795</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2767</v>
+        <v>0.4092</v>
       </c>
       <c r="G20" t="n">
         <v>1.9697</v>
@@ -2014,13 +2014,13 @@
         <v>2.9321</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2553</v>
+        <v>1.0032</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9322</v>
+        <v>0.5475</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3231</v>
+        <v>0.4557</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.7688</v>
+        <v>4.2161</v>
       </c>
       <c r="E21" t="n">
-        <v>3.0977</v>
+        <v>3.1939</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6711</v>
+        <v>1.0223</v>
       </c>
       <c r="G21" t="n">
         <v>1.118</v>
@@ -2092,13 +2092,13 @@
         <v>2.7489</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4963</v>
+        <v>0.9436</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5113</v>
+        <v>0.6075</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.015</v>
+        <v>0.3361</v>
       </c>
       <c r="V21" t="n">
         <v>0.3219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4891</v>
+        <v>2.9087</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9829</v>
+        <v>1.1753</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5062</v>
+        <v>1.7335</v>
       </c>
       <c r="G22" t="n">
         <v>3.1087</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4468</v>
+        <v>-0.0272</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1715</v>
+        <v>0.0558</v>
       </c>
       <c r="V22" t="n">
         <v>0.0104</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3743</v>
+        <v>2.0043</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1502</v>
+        <v>1.5733</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2241</v>
+        <v>0.431</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0217</v>
@@ -2248,13 +2248,13 @@
         <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>1.341</v>
+        <v>0.971</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2625</v>
+        <v>0.6855</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0786</v>
+        <v>0.2854</v>
       </c>
       <c r="V23" t="n">
         <v>0.9554</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7977</v>
+        <v>1.3567</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3193</v>
+        <v>-0.0123</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4785</v>
+        <v>1.369</v>
       </c>
       <c r="G24" t="n">
-        <v>1.14</v>
+        <v>1.0221</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0826</v>
+        <v>-0.9878</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9426</v>
+        <v>2.0099</v>
       </c>
       <c r="J24" t="n">
-        <v>2.2974</v>
+        <v>0.6483</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0216</v>
+        <v>-0.7527</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2758</v>
+        <v>1.401</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1575</v>
+        <v>0.3738</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0609</v>
+        <v>-0.2351</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2184</v>
+        <v>0.6089</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5656</v>
+        <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1526</v>
+        <v>0.1514</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1847</v>
+        <v>0.2557</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3373</v>
+        <v>-0.1043</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7783</v>
+        <v>1.0439</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0123</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7906</v>
+        <v>0.5324</v>
       </c>
       <c r="G25" t="n">
-        <v>1.0221</v>
+        <v>1.14</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9878</v>
+        <v>2.0826</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0099</v>
+        <v>-0.9426</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6483</v>
+        <v>2.2974</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7527</v>
+        <v>2.0216</v>
       </c>
       <c r="L25" t="n">
-        <v>1.401</v>
+        <v>0.2758</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3738</v>
+        <v>-1.1575</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2351</v>
+        <v>0.0609</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6089</v>
+        <v>-1.2184</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>2.5656</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4271</v>
+        <v>0.3988</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2557</v>
+        <v>0.0076</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6827</v>
+        <v>0.3912</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>I. BOU MIÑARRO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6251</v>
+        <v>1.0031</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6251</v>
+        <v>-0.5544</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.5576</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6251</v>
+        <v>0.769</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6251</v>
+        <v>-0.1861</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6251</v>
+        <v>1.012</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6251</v>
+        <v>0.1667</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.1098</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>-0.3528</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-0.0224</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-0.0558</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.416</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.9389999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="F27" t="n">
-        <v>1.355</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.769</v>
+        <v>-0.7852</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.0162</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1861</v>
+        <v>-0.8014</v>
       </c>
       <c r="J27" t="n">
-        <v>1.012</v>
+        <v>-0.576</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1667</v>
+        <v>-0.641</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.243</v>
+        <v>-0.2092</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1098</v>
+        <v>-0.0489</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3528</v>
+        <v>-0.1603</v>
       </c>
       <c r="P27" t="n">
         <v>-0.3665</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6096</v>
+        <v>0.1009</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4404</v>
+        <v>0.2334</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1692</v>
+        <v>-0.1325</v>
       </c>
       <c r="V27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="X27" t="n">
         <v>0.6231</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.3219</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.3011</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>I. BOU MIÑARRO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3482</v>
+        <v>0.6251</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2804</v>
+        <v>0.6251</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6286</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7852</v>
+        <v>0.6251</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0162</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8014</v>
+        <v>0.6251</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.576</v>
+        <v>0.6251</v>
       </c>
       <c r="K28" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.641</v>
+        <v>0.6251</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2092</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.0489</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.1603</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.3901</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.0551</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3351</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>40.1508</v>
+        <v>42.07380000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>28.033</v>
+        <v>28.0331</v>
       </c>
       <c r="F29" t="n">
-        <v>12.118</v>
+        <v>14.0412</v>
       </c>
       <c r="G29" t="n">
         <v>22.666</v>
@@ -2695,7 +2695,7 @@
         <v>20.5301</v>
       </c>
       <c r="L29" t="n">
-        <v>9.9397</v>
+        <v>9.939700000000002</v>
       </c>
       <c r="M29" t="n">
         <v>-7.803800000000001</v>
@@ -2704,7 +2704,7 @@
         <v>1.4947</v>
       </c>
       <c r="O29" t="n">
-        <v>-9.2986</v>
+        <v>-9.298599999999999</v>
       </c>
       <c r="P29" t="n">
         <v>3.6651</v>
@@ -2716,13 +2716,13 @@
         <v>20.1583</v>
       </c>
       <c r="S29" t="n">
-        <v>4.950899999999999</v>
+        <v>6.8741</v>
       </c>
       <c r="T29" t="n">
-        <v>4.200799999999999</v>
+        <v>4.2007</v>
       </c>
       <c r="U29" t="n">
-        <v>0.7501999999999998</v>
+        <v>2.6733</v>
       </c>
       <c r="V29" t="n">
         <v>8.868600000000001</v>
